--- a/Data/True_data/prior_data/final_trial_balance.xlsx
+++ b/Data/True_data/prior_data/final_trial_balance.xlsx
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>265.53</v>
+        <v>469.12</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>265.53</v>
+        <v>469.12</v>
       </c>
     </row>
     <row r="7">
@@ -566,13 +566,13 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>268.46</v>
+        <v>185.65</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>268.46</v>
+        <v>185.65</v>
       </c>
     </row>
     <row r="8">
@@ -600,10 +600,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>11.89</v>
+        <v>2.15</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-11.89</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="9">
@@ -628,13 +628,13 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>102.5</v>
+        <v>81.73</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>102.5</v>
+        <v>81.73</v>
       </c>
     </row>
     <row r="10">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>49.99</v>
+        <v>49.58</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>49.99</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="11">
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>513.04</v>
+        <v>364.65</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>513.04</v>
+        <v>364.65</v>
       </c>
     </row>
     <row r="12">
@@ -724,10 +724,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>166.24</v>
+        <v>110.4</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-166.24</v>
+        <v>-110.4</v>
       </c>
     </row>
     <row r="13">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>85.2</v>
+        <v>65.23</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>85.2</v>
+        <v>65.23</v>
       </c>
     </row>
     <row r="14">
@@ -786,10 +786,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>188.09</v>
+        <v>67.02</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-188.09</v>
+        <v>-67.02</v>
       </c>
     </row>
     <row r="15">
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>57.01</v>
+        <v>160.33</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-57.01</v>
+        <v>-160.33</v>
       </c>
     </row>
     <row r="16">
@@ -848,10 +848,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>53.47</v>
+        <v>27.59</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-53.47</v>
+        <v>-27.59</v>
       </c>
     </row>
     <row r="17">
@@ -879,10 +879,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>69.04000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-69.04000000000001</v>
+        <v>-73.5</v>
       </c>
     </row>
     <row r="18">
@@ -910,10 +910,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>199.04</v>
+        <v>294.82</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-199.04</v>
+        <v>-294.82</v>
       </c>
     </row>
     <row r="19">
@@ -941,10 +941,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>102.46</v>
+        <v>131.34</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-102.46</v>
+        <v>-131.34</v>
       </c>
     </row>
     <row r="20">
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>181.61</v>
+        <v>164.32</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-181.61</v>
+        <v>-164.32</v>
       </c>
     </row>
     <row r="21">
@@ -1003,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>255.89</v>
+        <v>184.48</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-255.89</v>
+        <v>-184.48</v>
       </c>
     </row>
   </sheetData>
